--- a/backend/data/financials_by_company/1497.HK.xlsx
+++ b/backend/data/financials_by_company/1497.HK.xlsx
@@ -687,624 +687,624 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>698289.517117</v>
+        <v>166162</v>
       </c>
       <c r="C2" t="n">
-        <v>0.223524</v>
+        <v>0.251</v>
       </c>
       <c r="D2" t="n">
-        <v>266855000</v>
+        <v>261262000</v>
       </c>
       <c r="E2" t="n">
-        <v>3124000</v>
+        <v>662000</v>
       </c>
       <c r="F2" t="n">
-        <v>3124000</v>
+        <v>662000</v>
       </c>
       <c r="G2" t="n">
-        <v>156295000</v>
+        <v>167353000</v>
       </c>
       <c r="H2" t="n">
-        <v>56416000</v>
+        <v>28414000</v>
       </c>
       <c r="I2" t="n">
-        <v>1037238000</v>
+        <v>780214000</v>
       </c>
       <c r="J2" t="n">
-        <v>269979000</v>
+        <v>261924000</v>
       </c>
       <c r="K2" t="n">
-        <v>213563000</v>
+        <v>233510000</v>
       </c>
       <c r="L2" t="n">
-        <v>-2349000</v>
+        <v>-1453000</v>
       </c>
       <c r="M2" t="n">
-        <v>6950000</v>
+        <v>3337000</v>
       </c>
       <c r="N2" t="n">
-        <v>4601000</v>
+        <v>1884000</v>
       </c>
       <c r="O2" t="n">
-        <v>153869289.517117</v>
+        <v>166857162</v>
       </c>
       <c r="P2" t="n">
-        <v>156295000</v>
+        <v>167353000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1843381000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>1267801000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>10364000</v>
+      </c>
       <c r="S2" t="n">
-        <v>213563000</v>
+        <v>233510000</v>
       </c>
       <c r="T2" t="n">
-        <v>461012000</v>
+        <v>465500000</v>
       </c>
       <c r="U2" t="n">
-        <v>461012000</v>
+        <v>465500000</v>
       </c>
       <c r="V2" t="n">
-        <v>0.34</v>
+        <v>0.353358</v>
       </c>
       <c r="W2" t="n">
-        <v>0.34</v>
+        <v>0.353358</v>
       </c>
       <c r="X2" t="n">
-        <v>156295000</v>
+        <v>164488000</v>
       </c>
       <c r="Y2" t="n">
-        <v>156295000</v>
+        <v>164488000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>2865000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
       <c r="AB2" t="n">
-        <v>156295000</v>
+        <v>167353000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-4135000</v>
+        <v>-5006000</v>
       </c>
       <c r="AD2" t="n">
-        <v>160430000</v>
+        <v>172359000</v>
       </c>
       <c r="AE2" t="n">
-        <v>160430000</v>
+        <v>172359000</v>
       </c>
       <c r="AF2" t="n">
-        <v>46183000</v>
+        <v>57814000</v>
       </c>
       <c r="AG2" t="n">
-        <v>206613000</v>
+        <v>230173000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-567000</v>
+        <v>-8232000</v>
       </c>
       <c r="AI2" t="n">
-        <v>314000</v>
+        <v>-1667000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-314000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>-192000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1859000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>-2349000</v>
+        <v>-1453000</v>
       </c>
       <c r="AM2" t="n">
-        <v>6950000</v>
+        <v>3337000</v>
       </c>
       <c r="AN2" t="n">
-        <v>4601000</v>
+        <v>1884000</v>
       </c>
       <c r="AO2" t="n">
-        <v>206619000</v>
+        <v>239196000</v>
       </c>
       <c r="AP2" t="n">
-        <v>806143000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+        <v>487587000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>17428000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>17428000</v>
+      </c>
       <c r="AS2" t="n">
-        <v>28544000</v>
+        <v>18982000</v>
       </c>
       <c r="AT2" t="n">
-        <v>810117000</v>
+        <v>333274000</v>
       </c>
       <c r="AU2" t="n">
-        <v>670774000</v>
+        <v>304828000</v>
       </c>
       <c r="AV2" t="n">
-        <v>139343000</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>28446000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>10364000</v>
+      </c>
       <c r="AX2" t="n">
-        <v>1012762000</v>
+        <v>726783000</v>
       </c>
       <c r="AY2" t="n">
-        <v>1037238000</v>
+        <v>780214000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2050000000</v>
+        <v>1506997000</v>
       </c>
       <c r="BA2" t="n">
-        <v>2050000000</v>
+        <v>1506997000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>479536.429026</v>
+        <v>393743.716124</v>
       </c>
       <c r="C3" t="n">
-        <v>0.225877</v>
+        <v>0.221827</v>
       </c>
       <c r="D3" t="n">
-        <v>314939000</v>
+        <v>301269000</v>
       </c>
       <c r="E3" t="n">
-        <v>2123000</v>
+        <v>1775000</v>
       </c>
       <c r="F3" t="n">
-        <v>2123000</v>
+        <v>1775000</v>
       </c>
       <c r="G3" t="n">
-        <v>201218000</v>
+        <v>191840000</v>
       </c>
       <c r="H3" t="n">
-        <v>40817000</v>
+        <v>36842000</v>
       </c>
       <c r="I3" t="n">
-        <v>969321000</v>
+        <v>851693000</v>
       </c>
       <c r="J3" t="n">
-        <v>317062000</v>
+        <v>303044000</v>
       </c>
       <c r="K3" t="n">
-        <v>276245000</v>
+        <v>266202000</v>
       </c>
       <c r="L3" t="n">
-        <v>471000</v>
+        <v>314000</v>
       </c>
       <c r="M3" t="n">
-        <v>2919000</v>
+        <v>1636000</v>
       </c>
       <c r="N3" t="n">
-        <v>3390000</v>
+        <v>1950000</v>
       </c>
       <c r="O3" t="n">
-        <v>199574536.429026</v>
+        <v>190458743.716124</v>
       </c>
       <c r="P3" t="n">
-        <v>201218000</v>
+        <v>191840000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1691251000</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>1466882000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>16937000</v>
+      </c>
       <c r="S3" t="n">
-        <v>276245000</v>
+        <v>266202000</v>
       </c>
       <c r="T3" t="n">
-        <v>427178000</v>
+        <v>465500000</v>
       </c>
       <c r="U3" t="n">
-        <v>427178000</v>
+        <v>465500000</v>
       </c>
       <c r="V3" t="n">
-        <v>0.46</v>
+        <v>0.404311</v>
       </c>
       <c r="W3" t="n">
-        <v>0.46</v>
+        <v>0.404311</v>
       </c>
       <c r="X3" t="n">
-        <v>197485000</v>
+        <v>188207000</v>
       </c>
       <c r="Y3" t="n">
-        <v>197485000</v>
+        <v>188207000</v>
       </c>
       <c r="Z3" t="n">
-        <v>3733000</v>
+        <v>3633000</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>201218000</v>
+        <v>191840000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-10370000</v>
+        <v>-14038000</v>
       </c>
       <c r="AD3" t="n">
-        <v>211588000</v>
+        <v>205878000</v>
       </c>
       <c r="AE3" t="n">
-        <v>211588000</v>
+        <v>205878000</v>
       </c>
       <c r="AF3" t="n">
-        <v>61738000</v>
+        <v>58688000</v>
       </c>
       <c r="AG3" t="n">
-        <v>273326000</v>
+        <v>264566000</v>
       </c>
       <c r="AH3" t="n">
         <v>-586000</v>
       </c>
       <c r="AI3" t="n">
-        <v>186000</v>
+        <v>320000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-186000</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+        <v>-320000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2205000</v>
+      </c>
       <c r="AL3" t="n">
-        <v>471000</v>
+        <v>314000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2919000</v>
+        <v>1636000</v>
       </c>
       <c r="AN3" t="n">
-        <v>3390000</v>
+        <v>1950000</v>
       </c>
       <c r="AO3" t="n">
-        <v>272986000</v>
+        <v>263063000</v>
       </c>
       <c r="AP3" t="n">
-        <v>721930000</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
+        <v>615189000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>22518000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>22518000</v>
+      </c>
       <c r="AS3" t="n">
-        <v>26384000</v>
+        <v>24320000</v>
       </c>
       <c r="AT3" t="n">
-        <v>722789000</v>
+        <v>615422000</v>
       </c>
       <c r="AU3" t="n">
-        <v>563283000</v>
+        <v>503879000</v>
       </c>
       <c r="AV3" t="n">
-        <v>159506000</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>111543000</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>16937000</v>
+      </c>
       <c r="AX3" t="n">
-        <v>994916000</v>
+        <v>878252000</v>
       </c>
       <c r="AY3" t="n">
-        <v>969321000</v>
+        <v>851693000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1964237000</v>
+        <v>1729945000</v>
       </c>
       <c r="BA3" t="n">
-        <v>1964237000</v>
+        <v>1729945000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>393743.716124</v>
+        <v>479536.429026</v>
       </c>
       <c r="C4" t="n">
-        <v>0.221827</v>
+        <v>0.225877</v>
       </c>
       <c r="D4" t="n">
-        <v>301269000</v>
+        <v>314939000</v>
       </c>
       <c r="E4" t="n">
-        <v>1775000</v>
+        <v>2123000</v>
       </c>
       <c r="F4" t="n">
-        <v>1775000</v>
+        <v>2123000</v>
       </c>
       <c r="G4" t="n">
-        <v>191840000</v>
+        <v>201218000</v>
       </c>
       <c r="H4" t="n">
-        <v>36842000</v>
+        <v>40817000</v>
       </c>
       <c r="I4" t="n">
-        <v>851693000</v>
+        <v>969321000</v>
       </c>
       <c r="J4" t="n">
-        <v>303044000</v>
+        <v>317062000</v>
       </c>
       <c r="K4" t="n">
-        <v>266202000</v>
+        <v>276245000</v>
       </c>
       <c r="L4" t="n">
-        <v>314000</v>
+        <v>471000</v>
       </c>
       <c r="M4" t="n">
-        <v>1636000</v>
+        <v>2919000</v>
       </c>
       <c r="N4" t="n">
-        <v>1950000</v>
+        <v>3390000</v>
       </c>
       <c r="O4" t="n">
-        <v>190458743.716124</v>
+        <v>199574536.429026</v>
       </c>
       <c r="P4" t="n">
-        <v>191840000</v>
+        <v>201218000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1466882000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>16937000</v>
-      </c>
+        <v>1691251000</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>266202000</v>
+        <v>276245000</v>
       </c>
       <c r="T4" t="n">
-        <v>465500000</v>
+        <v>427178000</v>
       </c>
       <c r="U4" t="n">
-        <v>465500000</v>
+        <v>427178000</v>
       </c>
       <c r="V4" t="n">
-        <v>0.404311</v>
+        <v>0.46</v>
       </c>
       <c r="W4" t="n">
-        <v>0.404311</v>
+        <v>0.46</v>
       </c>
       <c r="X4" t="n">
-        <v>188207000</v>
+        <v>197485000</v>
       </c>
       <c r="Y4" t="n">
-        <v>188207000</v>
+        <v>197485000</v>
       </c>
       <c r="Z4" t="n">
-        <v>3633000</v>
+        <v>3733000</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>191840000</v>
+        <v>201218000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-14038000</v>
+        <v>-10370000</v>
       </c>
       <c r="AD4" t="n">
-        <v>205878000</v>
+        <v>211588000</v>
       </c>
       <c r="AE4" t="n">
-        <v>205878000</v>
+        <v>211588000</v>
       </c>
       <c r="AF4" t="n">
-        <v>58688000</v>
+        <v>61738000</v>
       </c>
       <c r="AG4" t="n">
-        <v>264566000</v>
+        <v>273326000</v>
       </c>
       <c r="AH4" t="n">
         <v>-586000</v>
       </c>
       <c r="AI4" t="n">
-        <v>320000</v>
+        <v>186000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-320000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2205000</v>
-      </c>
+        <v>-186000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>314000</v>
+        <v>471000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1636000</v>
+        <v>2919000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1950000</v>
+        <v>3390000</v>
       </c>
       <c r="AO4" t="n">
-        <v>263063000</v>
+        <v>272986000</v>
       </c>
       <c r="AP4" t="n">
-        <v>615189000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>22518000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>22518000</v>
-      </c>
+        <v>721930000</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>24320000</v>
+        <v>26384000</v>
       </c>
       <c r="AT4" t="n">
-        <v>615422000</v>
+        <v>722789000</v>
       </c>
       <c r="AU4" t="n">
-        <v>503879000</v>
+        <v>563283000</v>
       </c>
       <c r="AV4" t="n">
-        <v>111543000</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>16937000</v>
-      </c>
+        <v>159506000</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>878252000</v>
+        <v>994916000</v>
       </c>
       <c r="AY4" t="n">
-        <v>851693000</v>
+        <v>969321000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1729945000</v>
+        <v>1964237000</v>
       </c>
       <c r="BA4" t="n">
-        <v>1729945000</v>
+        <v>1964237000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>166162</v>
+        <v>698289.517117</v>
       </c>
       <c r="C5" t="n">
-        <v>0.251</v>
+        <v>0.223524</v>
       </c>
       <c r="D5" t="n">
-        <v>261262000</v>
+        <v>266855000</v>
       </c>
       <c r="E5" t="n">
-        <v>662000</v>
+        <v>3124000</v>
       </c>
       <c r="F5" t="n">
-        <v>662000</v>
+        <v>3124000</v>
       </c>
       <c r="G5" t="n">
-        <v>167353000</v>
+        <v>156295000</v>
       </c>
       <c r="H5" t="n">
-        <v>28414000</v>
+        <v>56416000</v>
       </c>
       <c r="I5" t="n">
-        <v>780214000</v>
+        <v>1037238000</v>
       </c>
       <c r="J5" t="n">
-        <v>261924000</v>
+        <v>269979000</v>
       </c>
       <c r="K5" t="n">
-        <v>233510000</v>
+        <v>213563000</v>
       </c>
       <c r="L5" t="n">
-        <v>-1453000</v>
+        <v>-2349000</v>
       </c>
       <c r="M5" t="n">
-        <v>3337000</v>
+        <v>6950000</v>
       </c>
       <c r="N5" t="n">
-        <v>1884000</v>
+        <v>4601000</v>
       </c>
       <c r="O5" t="n">
-        <v>166857162</v>
+        <v>153869289.517117</v>
       </c>
       <c r="P5" t="n">
-        <v>167353000</v>
+        <v>156295000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1267801000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>10364000</v>
-      </c>
+        <v>1843381000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>233510000</v>
+        <v>213563000</v>
       </c>
       <c r="T5" t="n">
-        <v>465500000</v>
+        <v>461012000</v>
       </c>
       <c r="U5" t="n">
-        <v>465500000</v>
+        <v>461012000</v>
       </c>
       <c r="V5" t="n">
-        <v>0.353358</v>
+        <v>0.34</v>
       </c>
       <c r="W5" t="n">
-        <v>0.353358</v>
+        <v>0.34</v>
       </c>
       <c r="X5" t="n">
-        <v>164488000</v>
+        <v>156295000</v>
       </c>
       <c r="Y5" t="n">
-        <v>164488000</v>
+        <v>156295000</v>
       </c>
       <c r="Z5" t="n">
-        <v>2865000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>167353000</v>
+        <v>156295000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-5006000</v>
+        <v>-4135000</v>
       </c>
       <c r="AD5" t="n">
-        <v>172359000</v>
+        <v>160430000</v>
       </c>
       <c r="AE5" t="n">
-        <v>172359000</v>
+        <v>160430000</v>
       </c>
       <c r="AF5" t="n">
-        <v>57814000</v>
+        <v>46183000</v>
       </c>
       <c r="AG5" t="n">
-        <v>230173000</v>
+        <v>206613000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-8232000</v>
+        <v>-567000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1667000</v>
+        <v>314000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-192000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1859000</v>
-      </c>
+        <v>-314000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>-1453000</v>
+        <v>-2349000</v>
       </c>
       <c r="AM5" t="n">
-        <v>3337000</v>
+        <v>6950000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1884000</v>
+        <v>4601000</v>
       </c>
       <c r="AO5" t="n">
-        <v>239196000</v>
+        <v>206619000</v>
       </c>
       <c r="AP5" t="n">
-        <v>487587000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>17428000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>17428000</v>
-      </c>
+        <v>806143000</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>18982000</v>
+        <v>28544000</v>
       </c>
       <c r="AT5" t="n">
-        <v>333274000</v>
+        <v>810117000</v>
       </c>
       <c r="AU5" t="n">
-        <v>304828000</v>
+        <v>670774000</v>
       </c>
       <c r="AV5" t="n">
-        <v>28446000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>10364000</v>
-      </c>
+        <v>139343000</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>726783000</v>
+        <v>1012762000</v>
       </c>
       <c r="AY5" t="n">
-        <v>780214000</v>
+        <v>1037238000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1506997000</v>
+        <v>2050000000</v>
       </c>
       <c r="BA5" t="n">
-        <v>1506997000</v>
+        <v>2050000000</v>
       </c>
     </row>
   </sheetData>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>465500000</v>
@@ -1679,200 +1679,200 @@
         <v>465500000</v>
       </c>
       <c r="D2" t="n">
-        <v>130315000</v>
+        <v>32691000</v>
       </c>
       <c r="E2" t="n">
-        <v>666595000</v>
+        <v>260915000</v>
       </c>
       <c r="F2" t="n">
-        <v>745742000</v>
+        <v>336953000</v>
       </c>
       <c r="G2" t="n">
-        <v>402043000</v>
+        <v>181322000</v>
       </c>
       <c r="H2" t="n">
-        <v>666595000</v>
+        <v>260915000</v>
       </c>
       <c r="I2" t="n">
-        <v>130315000</v>
+        <v>32691000</v>
       </c>
       <c r="J2" t="n">
-        <v>745742000</v>
+        <v>336953000</v>
       </c>
       <c r="K2" t="n">
-        <v>745742000</v>
+        <v>336953000</v>
       </c>
       <c r="L2" t="n">
-        <v>768244000</v>
+        <v>353137000</v>
       </c>
       <c r="M2" t="n">
-        <v>22502000</v>
+        <v>16184000</v>
       </c>
       <c r="N2" t="n">
-        <v>745742000</v>
+        <v>336953000</v>
       </c>
       <c r="O2" t="n">
-        <v>-94073000</v>
+        <v>4049000</v>
       </c>
       <c r="P2" t="n">
-        <v>216933000</v>
+        <v>56014000</v>
       </c>
       <c r="Q2" t="n">
-        <v>433389000</v>
+        <v>156080000</v>
       </c>
       <c r="R2" t="n">
-        <v>93100000</v>
+        <v>86700000</v>
       </c>
       <c r="S2" t="n">
-        <v>93100000</v>
+        <v>86700000</v>
       </c>
       <c r="T2" t="n">
-        <v>718370000</v>
+        <v>443589000</v>
       </c>
       <c r="U2" t="n">
-        <v>106898000</v>
+        <v>19332000</v>
       </c>
       <c r="V2" t="n">
-        <v>1850000</v>
+        <v>2285000</v>
       </c>
       <c r="W2" t="n">
-        <v>105048000</v>
+        <v>17047000</v>
       </c>
       <c r="X2" t="n">
-        <v>105048000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>17047000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
       <c r="Z2" t="n">
-        <v>611472000</v>
+        <v>424257000</v>
       </c>
       <c r="AA2" t="n">
-        <v>32348000</v>
+        <v>17897000</v>
       </c>
       <c r="AB2" t="n">
-        <v>25267000</v>
+        <v>15644000</v>
       </c>
       <c r="AC2" t="n">
-        <v>25267000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>15644000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
       <c r="AE2" t="n">
-        <v>54025000</v>
+        <v>38682000</v>
       </c>
       <c r="AF2" t="n">
-        <v>198353000</v>
+        <v>188316000</v>
       </c>
       <c r="AG2" t="n">
-        <v>93665000</v>
+        <v>66950000</v>
       </c>
       <c r="AH2" t="n">
-        <v>37793000</v>
+        <v>58899000</v>
       </c>
       <c r="AI2" t="n">
-        <v>66895000</v>
+        <v>62467000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1486614000</v>
+        <v>796726000</v>
       </c>
       <c r="AK2" t="n">
-        <v>473099000</v>
+        <v>191147000</v>
       </c>
       <c r="AL2" t="n">
-        <v>23365000</v>
+        <v>6862000</v>
       </c>
       <c r="AM2" t="n">
-        <v>51227000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>36939000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>35948000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>991000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+        <v>16313000</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
       <c r="AS2" t="n">
-        <v>79147000</v>
+        <v>76038000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1982000</v>
+        <v>873000</v>
       </c>
       <c r="AU2" t="n">
-        <v>77165000</v>
+        <v>75165000</v>
       </c>
       <c r="AV2" t="n">
-        <v>282421000</v>
+        <v>91934000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-123592000</v>
+        <v>-46179000</v>
       </c>
       <c r="AX2" t="n">
-        <v>406013000</v>
+        <v>138113000</v>
       </c>
       <c r="AY2" t="n">
-        <v>2753000</v>
+        <v>1292000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>112185000</v>
+        <v>48929000</v>
       </c>
       <c r="BA2" t="n">
-        <v>291075000</v>
+        <v>87892000</v>
       </c>
       <c r="BB2" t="n">
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1013515000</v>
+        <v>605579000</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="BE2" t="n">
-        <v>80255000</v>
+        <v>76175000</v>
       </c>
       <c r="BF2" t="n">
-        <v>353198000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>-617000</v>
-      </c>
+        <v>279742000</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="n">
-        <v>237000</v>
+        <v>101000</v>
       </c>
       <c r="BI2" t="n">
-        <v>99735000</v>
+        <v>69932000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>40561000</v>
+        <v>33360000</v>
       </c>
       <c r="BK2" t="n">
-        <v>213282000</v>
+        <v>176349000</v>
       </c>
       <c r="BL2" t="n">
-        <v>30691000</v>
+        <v>24956000</v>
       </c>
       <c r="BM2" t="n">
-        <v>36496000</v>
+        <v>14769000</v>
       </c>
       <c r="BN2" t="n">
-        <v>92367000</v>
+        <v>38442000</v>
       </c>
       <c r="BO2" t="n">
-        <v>420508000</v>
+        <v>169495000</v>
       </c>
       <c r="BP2" t="inlineStr"/>
       <c r="BQ2" t="n">
-        <v>420508000</v>
+        <v>169495000</v>
       </c>
       <c r="BR2" t="n">
-        <v>420508000</v>
+        <v>169495000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>465500000</v>
@@ -1881,196 +1881,202 @@
         <v>465500000</v>
       </c>
       <c r="D3" t="n">
-        <v>137678000</v>
+        <v>26921000</v>
       </c>
       <c r="E3" t="n">
-        <v>693226000</v>
+        <v>377956000</v>
       </c>
       <c r="F3" t="n">
-        <v>769671000</v>
+        <v>454396000</v>
       </c>
       <c r="G3" t="n">
-        <v>594387000</v>
+        <v>280178000</v>
       </c>
       <c r="H3" t="n">
-        <v>693226000</v>
+        <v>377956000</v>
       </c>
       <c r="I3" t="n">
-        <v>137678000</v>
+        <v>26921000</v>
       </c>
       <c r="J3" t="n">
-        <v>769671000</v>
+        <v>454396000</v>
       </c>
       <c r="K3" t="n">
-        <v>769671000</v>
+        <v>454396000</v>
       </c>
       <c r="L3" t="n">
-        <v>796927000</v>
+        <v>472010000</v>
       </c>
       <c r="M3" t="n">
-        <v>27256000</v>
+        <v>17614000</v>
       </c>
       <c r="N3" t="n">
-        <v>769671000</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>454396000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>9302000</v>
+      </c>
       <c r="P3" t="n">
-        <v>167313000</v>
+        <v>136717000</v>
       </c>
       <c r="Q3" t="n">
-        <v>433389000</v>
+        <v>156430000</v>
       </c>
       <c r="R3" t="n">
-        <v>93100000</v>
+        <v>86700000</v>
       </c>
       <c r="S3" t="n">
-        <v>93100000</v>
+        <v>86700000</v>
       </c>
       <c r="T3" t="n">
-        <v>673066000</v>
+        <v>506344000</v>
       </c>
       <c r="U3" t="n">
-        <v>112946000</v>
+        <v>13199000</v>
       </c>
       <c r="V3" t="n">
-        <v>1659000</v>
+        <v>1935000</v>
       </c>
       <c r="W3" t="n">
-        <v>111287000</v>
+        <v>11264000</v>
       </c>
       <c r="X3" t="n">
-        <v>111287000</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+        <v>11264000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
       <c r="Z3" t="n">
-        <v>560120000</v>
+        <v>493145000</v>
       </c>
       <c r="AA3" t="n">
-        <v>28381000</v>
+        <v>23274000</v>
       </c>
       <c r="AB3" t="n">
-        <v>26391000</v>
+        <v>15657000</v>
       </c>
       <c r="AC3" t="n">
-        <v>26391000</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
+        <v>15657000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE3" t="n">
-        <v>53774000</v>
+        <v>49477000</v>
       </c>
       <c r="AF3" t="n">
-        <v>194290000</v>
+        <v>206252000</v>
       </c>
       <c r="AG3" t="n">
-        <v>98993000</v>
+        <v>85852000</v>
       </c>
       <c r="AH3" t="n">
-        <v>32772000</v>
+        <v>56313000</v>
       </c>
       <c r="AI3" t="n">
-        <v>62525000</v>
+        <v>64087000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1469993000</v>
+        <v>978354000</v>
       </c>
       <c r="AK3" t="n">
-        <v>315486000</v>
+        <v>205031000</v>
       </c>
       <c r="AL3" t="n">
-        <v>14698000</v>
+        <v>4679000</v>
       </c>
       <c r="AM3" t="n">
-        <v>34371000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
+        <v>36130000</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
       <c r="AS3" t="n">
-        <v>76445000</v>
+        <v>76440000</v>
       </c>
       <c r="AT3" t="n">
-        <v>1280000</v>
+        <v>1275000</v>
       </c>
       <c r="AU3" t="n">
         <v>75165000</v>
       </c>
       <c r="AV3" t="n">
-        <v>189972000</v>
+        <v>87782000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-86134000</v>
+        <v>-63018000</v>
       </c>
       <c r="AX3" t="n">
-        <v>276106000</v>
+        <v>150800000</v>
       </c>
       <c r="AY3" t="n">
-        <v>1442000</v>
+        <v>930000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>67310000</v>
+        <v>57568000</v>
       </c>
       <c r="BA3" t="n">
-        <v>207354000</v>
+        <v>92302000</v>
       </c>
       <c r="BB3" t="n">
         <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1154507000</v>
+        <v>773323000</v>
       </c>
       <c r="BD3" t="n">
-        <v>8074000</v>
+        <v>1600000</v>
       </c>
       <c r="BE3" t="n">
-        <v>142416000</v>
+        <v>63937000</v>
       </c>
       <c r="BF3" t="n">
-        <v>360362000</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>-1388000</v>
-      </c>
+        <v>271795000</v>
+      </c>
+      <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="n">
-        <v>94000</v>
+        <v>233000</v>
       </c>
       <c r="BI3" t="n">
-        <v>89266000</v>
+        <v>94799000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>49354000</v>
+        <v>36467000</v>
       </c>
       <c r="BK3" t="n">
-        <v>223036000</v>
+        <v>140296000</v>
       </c>
       <c r="BL3" t="n">
-        <v>3661000</v>
+        <v>3387000</v>
       </c>
       <c r="BM3" t="n">
-        <v>19603000</v>
+        <v>13956000</v>
       </c>
       <c r="BN3" t="n">
-        <v>83298000</v>
+        <v>62834000</v>
       </c>
       <c r="BO3" t="n">
-        <v>537093000</v>
-      </c>
-      <c r="BP3" t="inlineStr"/>
+        <v>355814000</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>4996000</v>
+      </c>
       <c r="BQ3" t="n">
-        <v>537093000</v>
+        <v>350818000</v>
       </c>
       <c r="BR3" t="n">
-        <v>537093000</v>
+        <v>350818000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>465500000</v>
@@ -2079,202 +2085,196 @@
         <v>465500000</v>
       </c>
       <c r="D4" t="n">
-        <v>26921000</v>
+        <v>137678000</v>
       </c>
       <c r="E4" t="n">
-        <v>377956000</v>
+        <v>693226000</v>
       </c>
       <c r="F4" t="n">
-        <v>454396000</v>
+        <v>769671000</v>
       </c>
       <c r="G4" t="n">
-        <v>280178000</v>
+        <v>594387000</v>
       </c>
       <c r="H4" t="n">
-        <v>377956000</v>
+        <v>693226000</v>
       </c>
       <c r="I4" t="n">
-        <v>26921000</v>
+        <v>137678000</v>
       </c>
       <c r="J4" t="n">
-        <v>454396000</v>
+        <v>769671000</v>
       </c>
       <c r="K4" t="n">
-        <v>454396000</v>
+        <v>769671000</v>
       </c>
       <c r="L4" t="n">
-        <v>472010000</v>
+        <v>796927000</v>
       </c>
       <c r="M4" t="n">
-        <v>17614000</v>
+        <v>27256000</v>
       </c>
       <c r="N4" t="n">
-        <v>454396000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>9302000</v>
-      </c>
+        <v>769671000</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>136717000</v>
+        <v>167313000</v>
       </c>
       <c r="Q4" t="n">
-        <v>156430000</v>
+        <v>433389000</v>
       </c>
       <c r="R4" t="n">
-        <v>86700000</v>
+        <v>93100000</v>
       </c>
       <c r="S4" t="n">
-        <v>86700000</v>
+        <v>93100000</v>
       </c>
       <c r="T4" t="n">
-        <v>506344000</v>
+        <v>673066000</v>
       </c>
       <c r="U4" t="n">
-        <v>13199000</v>
+        <v>112946000</v>
       </c>
       <c r="V4" t="n">
-        <v>1935000</v>
+        <v>1659000</v>
       </c>
       <c r="W4" t="n">
-        <v>11264000</v>
+        <v>111287000</v>
       </c>
       <c r="X4" t="n">
-        <v>11264000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
+        <v>111287000</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>493145000</v>
+        <v>560120000</v>
       </c>
       <c r="AA4" t="n">
-        <v>23274000</v>
+        <v>28381000</v>
       </c>
       <c r="AB4" t="n">
-        <v>15657000</v>
+        <v>26391000</v>
       </c>
       <c r="AC4" t="n">
-        <v>15657000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
+        <v>26391000</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>49477000</v>
+        <v>53774000</v>
       </c>
       <c r="AF4" t="n">
-        <v>206252000</v>
+        <v>194290000</v>
       </c>
       <c r="AG4" t="n">
-        <v>85852000</v>
+        <v>98993000</v>
       </c>
       <c r="AH4" t="n">
-        <v>56313000</v>
+        <v>32772000</v>
       </c>
       <c r="AI4" t="n">
-        <v>64087000</v>
+        <v>62525000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>978354000</v>
+        <v>1469993000</v>
       </c>
       <c r="AK4" t="n">
-        <v>205031000</v>
+        <v>315486000</v>
       </c>
       <c r="AL4" t="n">
-        <v>4679000</v>
+        <v>14698000</v>
       </c>
       <c r="AM4" t="n">
-        <v>36130000</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>34371000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
       <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>76440000</v>
+        <v>76445000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1275000</v>
+        <v>1280000</v>
       </c>
       <c r="AU4" t="n">
         <v>75165000</v>
       </c>
       <c r="AV4" t="n">
-        <v>87782000</v>
+        <v>189972000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-63018000</v>
+        <v>-86134000</v>
       </c>
       <c r="AX4" t="n">
-        <v>150800000</v>
+        <v>276106000</v>
       </c>
       <c r="AY4" t="n">
-        <v>930000</v>
+        <v>1442000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>57568000</v>
+        <v>67310000</v>
       </c>
       <c r="BA4" t="n">
-        <v>92302000</v>
+        <v>207354000</v>
       </c>
       <c r="BB4" t="n">
         <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>773323000</v>
+        <v>1154507000</v>
       </c>
       <c r="BD4" t="n">
-        <v>1600000</v>
+        <v>8074000</v>
       </c>
       <c r="BE4" t="n">
-        <v>63937000</v>
+        <v>142416000</v>
       </c>
       <c r="BF4" t="n">
-        <v>271795000</v>
-      </c>
-      <c r="BG4" t="inlineStr"/>
+        <v>360362000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-1388000</v>
+      </c>
       <c r="BH4" t="n">
-        <v>233000</v>
+        <v>94000</v>
       </c>
       <c r="BI4" t="n">
-        <v>94799000</v>
+        <v>89266000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>36467000</v>
+        <v>49354000</v>
       </c>
       <c r="BK4" t="n">
-        <v>140296000</v>
+        <v>223036000</v>
       </c>
       <c r="BL4" t="n">
-        <v>3387000</v>
+        <v>3661000</v>
       </c>
       <c r="BM4" t="n">
-        <v>13956000</v>
+        <v>19603000</v>
       </c>
       <c r="BN4" t="n">
-        <v>62834000</v>
+        <v>83298000</v>
       </c>
       <c r="BO4" t="n">
-        <v>355814000</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>4996000</v>
-      </c>
+        <v>537093000</v>
+      </c>
+      <c r="BP4" t="inlineStr"/>
       <c r="BQ4" t="n">
-        <v>350818000</v>
+        <v>537093000</v>
       </c>
       <c r="BR4" t="n">
-        <v>350818000</v>
+        <v>537093000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>465500000</v>
@@ -2283,195 +2283,195 @@
         <v>465500000</v>
       </c>
       <c r="D5" t="n">
-        <v>32691000</v>
+        <v>130315000</v>
       </c>
       <c r="E5" t="n">
-        <v>260915000</v>
+        <v>666595000</v>
       </c>
       <c r="F5" t="n">
-        <v>336953000</v>
+        <v>745742000</v>
       </c>
       <c r="G5" t="n">
-        <v>181322000</v>
+        <v>402043000</v>
       </c>
       <c r="H5" t="n">
-        <v>260915000</v>
+        <v>666595000</v>
       </c>
       <c r="I5" t="n">
-        <v>32691000</v>
+        <v>130315000</v>
       </c>
       <c r="J5" t="n">
-        <v>336953000</v>
+        <v>745742000</v>
       </c>
       <c r="K5" t="n">
-        <v>336953000</v>
+        <v>745742000</v>
       </c>
       <c r="L5" t="n">
-        <v>353137000</v>
+        <v>768244000</v>
       </c>
       <c r="M5" t="n">
-        <v>16184000</v>
+        <v>22502000</v>
       </c>
       <c r="N5" t="n">
-        <v>336953000</v>
+        <v>745742000</v>
       </c>
       <c r="O5" t="n">
-        <v>4049000</v>
+        <v>-94073000</v>
       </c>
       <c r="P5" t="n">
-        <v>56014000</v>
+        <v>216933000</v>
       </c>
       <c r="Q5" t="n">
-        <v>156080000</v>
+        <v>433389000</v>
       </c>
       <c r="R5" t="n">
-        <v>86700000</v>
+        <v>93100000</v>
       </c>
       <c r="S5" t="n">
-        <v>86700000</v>
+        <v>93100000</v>
       </c>
       <c r="T5" t="n">
-        <v>443589000</v>
+        <v>718370000</v>
       </c>
       <c r="U5" t="n">
-        <v>19332000</v>
+        <v>106898000</v>
       </c>
       <c r="V5" t="n">
-        <v>2285000</v>
+        <v>1850000</v>
       </c>
       <c r="W5" t="n">
-        <v>17047000</v>
+        <v>105048000</v>
       </c>
       <c r="X5" t="n">
-        <v>17047000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
+        <v>105048000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>424257000</v>
+        <v>611472000</v>
       </c>
       <c r="AA5" t="n">
-        <v>17897000</v>
+        <v>32348000</v>
       </c>
       <c r="AB5" t="n">
-        <v>15644000</v>
+        <v>25267000</v>
       </c>
       <c r="AC5" t="n">
-        <v>15644000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
+        <v>25267000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>38682000</v>
+        <v>54025000</v>
       </c>
       <c r="AF5" t="n">
-        <v>188316000</v>
+        <v>198353000</v>
       </c>
       <c r="AG5" t="n">
-        <v>66950000</v>
+        <v>93665000</v>
       </c>
       <c r="AH5" t="n">
-        <v>58899000</v>
+        <v>37793000</v>
       </c>
       <c r="AI5" t="n">
-        <v>62467000</v>
+        <v>66895000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>796726000</v>
+        <v>1486614000</v>
       </c>
       <c r="AK5" t="n">
-        <v>191147000</v>
+        <v>473099000</v>
       </c>
       <c r="AL5" t="n">
-        <v>6862000</v>
+        <v>23365000</v>
       </c>
       <c r="AM5" t="n">
-        <v>16313000</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
+        <v>51227000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>36939000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>35948000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>991000</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>76038000</v>
+        <v>79147000</v>
       </c>
       <c r="AT5" t="n">
-        <v>873000</v>
+        <v>1982000</v>
       </c>
       <c r="AU5" t="n">
-        <v>75165000</v>
+        <v>77165000</v>
       </c>
       <c r="AV5" t="n">
-        <v>91934000</v>
+        <v>282421000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-46179000</v>
+        <v>-123592000</v>
       </c>
       <c r="AX5" t="n">
-        <v>138113000</v>
+        <v>406013000</v>
       </c>
       <c r="AY5" t="n">
-        <v>1292000</v>
+        <v>2753000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>48929000</v>
+        <v>112185000</v>
       </c>
       <c r="BA5" t="n">
-        <v>87892000</v>
+        <v>291075000</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>605579000</v>
+        <v>1013515000</v>
       </c>
       <c r="BD5" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>76175000</v>
+        <v>80255000</v>
       </c>
       <c r="BF5" t="n">
-        <v>279742000</v>
-      </c>
-      <c r="BG5" t="inlineStr"/>
+        <v>353198000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-617000</v>
+      </c>
       <c r="BH5" t="n">
-        <v>101000</v>
+        <v>237000</v>
       </c>
       <c r="BI5" t="n">
-        <v>69932000</v>
+        <v>99735000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>33360000</v>
+        <v>40561000</v>
       </c>
       <c r="BK5" t="n">
-        <v>176349000</v>
+        <v>213282000</v>
       </c>
       <c r="BL5" t="n">
-        <v>24956000</v>
+        <v>30691000</v>
       </c>
       <c r="BM5" t="n">
-        <v>14769000</v>
+        <v>36496000</v>
       </c>
       <c r="BN5" t="n">
-        <v>38442000</v>
+        <v>92367000</v>
       </c>
       <c r="BO5" t="n">
-        <v>169495000</v>
+        <v>420508000</v>
       </c>
       <c r="BP5" t="inlineStr"/>
       <c r="BQ5" t="n">
-        <v>169495000</v>
+        <v>420508000</v>
       </c>
       <c r="BR5" t="n">
-        <v>169495000</v>
+        <v>420508000</v>
       </c>
     </row>
   </sheetData>
@@ -2742,200 +2742,204 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>143192000</v>
+        <v>188966000</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-129597000</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>55371000</v>
       </c>
       <c r="E2" t="n">
-        <v>-94073000</v>
+        <v>40400000</v>
       </c>
       <c r="F2" t="n">
-        <v>-114191000</v>
+        <v>-24806000</v>
       </c>
       <c r="G2" t="n">
-        <v>420508000</v>
+        <v>169495000</v>
       </c>
       <c r="H2" t="n">
-        <v>537093000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-227000</v>
-      </c>
+        <v>150573000</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>-116358000</v>
+        <v>18922000</v>
       </c>
       <c r="K2" t="n">
-        <v>-240020000</v>
+        <v>-148400000</v>
       </c>
       <c r="L2" t="n">
-        <v>485000</v>
+        <v>3600000</v>
       </c>
       <c r="M2" t="n">
-        <v>-6950000</v>
+        <v>-3805000</v>
       </c>
       <c r="N2" t="n">
-        <v>-100077000</v>
+        <v>-100000000</v>
       </c>
       <c r="O2" t="n">
-        <v>-100077000</v>
+        <v>-100000000</v>
       </c>
       <c r="P2" t="n">
-        <v>-94073000</v>
+        <v>40400000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-94073000</v>
+        <v>40400000</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-74226000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-74226000</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-129597000</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>55371000</v>
       </c>
       <c r="V2" t="n">
-        <v>-133721000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>-46450000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1492000</v>
+      </c>
       <c r="X2" t="n">
-        <v>-15552000</v>
+        <v>48554000</v>
       </c>
       <c r="Y2" t="n">
-        <v>697009000</v>
+        <v>575894000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-712561000</v>
+        <v>-527340000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-4000000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>-71717000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2100000</v>
+      </c>
       <c r="AC2" t="n">
-        <v>-4000000</v>
+        <v>-73817000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-114169000</v>
+        <v>-24779000</v>
       </c>
       <c r="AE2" t="n">
-        <v>22000</v>
+        <v>27000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-114191000</v>
+        <v>-24806000</v>
       </c>
       <c r="AG2" t="n">
-        <v>257383000</v>
+        <v>213772000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-48342000</v>
+        <v>-39642000</v>
       </c>
       <c r="AI2" t="n">
-        <v>35592000</v>
+        <v>-28074000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3967000</v>
+        <v>1716000</v>
       </c>
       <c r="AK2" t="n">
-        <v>34609000</v>
+        <v>28460000</v>
       </c>
       <c r="AL2" t="n">
-        <v>11288000</v>
+        <v>-28160000</v>
       </c>
       <c r="AM2" t="n">
-        <v>8229000</v>
+        <v>7579000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-22501000</v>
+        <v>-37669000</v>
       </c>
       <c r="AO2" t="n">
-        <v>6950000</v>
+        <v>1511000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>21813000</v>
       </c>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>56416000</v>
+        <v>28414000</v>
       </c>
       <c r="AS2" t="n">
-        <v>546000</v>
+        <v>272000</v>
       </c>
       <c r="AT2" t="n">
-        <v>55870000</v>
+        <v>28142000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-2810000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>214000</v>
-      </c>
+        <v>-2329000</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>-314000</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+        <v>-159000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-33000</v>
+      </c>
       <c r="AY2" t="n">
-        <v>206613000</v>
+        <v>230173000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>99000000</v>
+        <v>283401000</v>
       </c>
       <c r="C3" t="n">
-        <v>-18000</v>
+        <v>-12183000</v>
       </c>
       <c r="D3" t="n">
-        <v>18000</v>
+        <v>12183000</v>
       </c>
       <c r="E3" t="n">
-        <v>283029000</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-24351000</v>
+        <v>-22478000</v>
       </c>
       <c r="G3" t="n">
-        <v>537093000</v>
+        <v>350818000</v>
       </c>
       <c r="H3" t="n">
-        <v>350818000</v>
+        <v>169495000</v>
       </c>
       <c r="I3" t="n">
-        <v>-1657000</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>187932000</v>
+        <v>181323000</v>
       </c>
       <c r="K3" t="n">
-        <v>81999000</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>-103532000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-1000000</v>
+      </c>
       <c r="M3" t="n">
-        <v>-2919000</v>
+        <v>-1636000</v>
       </c>
       <c r="N3" t="n">
-        <v>-160000000</v>
+        <v>-80000000</v>
       </c>
       <c r="O3" t="n">
-        <v>-160000000</v>
+        <v>-80000000</v>
       </c>
       <c r="P3" t="n">
-        <v>283029000</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>283029000</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -2944,151 +2948,151 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-18000</v>
+        <v>-12183000</v>
       </c>
       <c r="U3" t="n">
-        <v>18000</v>
+        <v>12183000</v>
       </c>
       <c r="V3" t="n">
-        <v>-17418000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>-21024000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
       <c r="X3" t="n">
-        <v>6933000</v>
+        <v>-3541000</v>
       </c>
       <c r="Y3" t="n">
-        <v>754933000</v>
+        <v>551459000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-748000000</v>
+        <v>-555000000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>4995000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>4995000</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-24351000</v>
+        <v>-22478000</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-24351000</v>
+        <v>-22478000</v>
       </c>
       <c r="AG3" t="n">
-        <v>123351000</v>
+        <v>305879000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-88921000</v>
+        <v>-88072000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-111137000</v>
+        <v>85862000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>5107000</v>
+        <v>5377000</v>
       </c>
       <c r="AK3" t="n">
-        <v>42379000</v>
+        <v>36654000</v>
       </c>
       <c r="AL3" t="n">
-        <v>26947000</v>
+        <v>32191000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-88567000</v>
+        <v>7947000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-97003000</v>
+        <v>3693000</v>
       </c>
       <c r="AO3" t="n">
-        <v>2919000</v>
+        <v>1163000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4816000</v>
+        <v>5253000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1361000</v>
+        <v>-779000</v>
       </c>
       <c r="AR3" t="n">
-        <v>40817000</v>
+        <v>36842000</v>
       </c>
       <c r="AS3" t="n">
-        <v>653000</v>
+        <v>540000</v>
       </c>
       <c r="AT3" t="n">
-        <v>40164000</v>
+        <v>36302000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-1937000</v>
+        <v>-1455000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1668000</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-186000</v>
+        <v>60000</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>-380000</v>
       </c>
       <c r="AY3" t="n">
-        <v>273326000</v>
+        <v>264566000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>283401000</v>
+        <v>99000000</v>
       </c>
       <c r="C4" t="n">
-        <v>-12183000</v>
+        <v>-18000</v>
       </c>
       <c r="D4" t="n">
-        <v>12183000</v>
+        <v>18000</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>283029000</v>
       </c>
       <c r="F4" t="n">
-        <v>-22478000</v>
+        <v>-24351000</v>
       </c>
       <c r="G4" t="n">
+        <v>537093000</v>
+      </c>
+      <c r="H4" t="n">
         <v>350818000</v>
       </c>
-      <c r="H4" t="n">
-        <v>169495000</v>
-      </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-1657000</v>
       </c>
       <c r="J4" t="n">
-        <v>181323000</v>
+        <v>187932000</v>
       </c>
       <c r="K4" t="n">
-        <v>-103532000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-1000000</v>
-      </c>
+        <v>81999000</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-1636000</v>
+        <v>-2919000</v>
       </c>
       <c r="N4" t="n">
-        <v>-80000000</v>
+        <v>-160000000</v>
       </c>
       <c r="O4" t="n">
-        <v>-80000000</v>
+        <v>-160000000</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>283029000</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>283029000</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -3097,249 +3101,245 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-12183000</v>
+        <v>-18000</v>
       </c>
       <c r="U4" t="n">
-        <v>12183000</v>
+        <v>18000</v>
       </c>
       <c r="V4" t="n">
-        <v>-21024000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
+        <v>-17418000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>-3541000</v>
+        <v>6933000</v>
       </c>
       <c r="Y4" t="n">
-        <v>551459000</v>
+        <v>754933000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-555000000</v>
+        <v>-748000000</v>
       </c>
       <c r="AA4" t="n">
-        <v>4995000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>4995000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-22478000</v>
+        <v>-24351000</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-22478000</v>
+        <v>-24351000</v>
       </c>
       <c r="AG4" t="n">
-        <v>305879000</v>
+        <v>123351000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-88072000</v>
+        <v>-88921000</v>
       </c>
       <c r="AI4" t="n">
-        <v>85862000</v>
+        <v>-111137000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5377000</v>
+        <v>5107000</v>
       </c>
       <c r="AK4" t="n">
-        <v>36654000</v>
+        <v>42379000</v>
       </c>
       <c r="AL4" t="n">
-        <v>32191000</v>
+        <v>26947000</v>
       </c>
       <c r="AM4" t="n">
-        <v>7947000</v>
+        <v>-88567000</v>
       </c>
       <c r="AN4" t="n">
-        <v>3693000</v>
+        <v>-97003000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1163000</v>
+        <v>2919000</v>
       </c>
       <c r="AP4" t="n">
-        <v>5253000</v>
+        <v>4816000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-779000</v>
+        <v>1361000</v>
       </c>
       <c r="AR4" t="n">
-        <v>36842000</v>
+        <v>40817000</v>
       </c>
       <c r="AS4" t="n">
-        <v>540000</v>
+        <v>653000</v>
       </c>
       <c r="AT4" t="n">
-        <v>36302000</v>
+        <v>40164000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-1455000</v>
+        <v>-1937000</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1668000</v>
       </c>
       <c r="AW4" t="n">
-        <v>60000</v>
+        <v>-186000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-380000</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>264566000</v>
+        <v>273326000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>188966000</v>
+        <v>143192000</v>
       </c>
       <c r="C5" t="n">
-        <v>-129597000</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>55371000</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>40400000</v>
+        <v>-94073000</v>
       </c>
       <c r="F5" t="n">
-        <v>-24806000</v>
+        <v>-114191000</v>
       </c>
       <c r="G5" t="n">
-        <v>169495000</v>
+        <v>420508000</v>
       </c>
       <c r="H5" t="n">
-        <v>150573000</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>537093000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-227000</v>
+      </c>
       <c r="J5" t="n">
-        <v>18922000</v>
+        <v>-116358000</v>
       </c>
       <c r="K5" t="n">
-        <v>-148400000</v>
+        <v>-240020000</v>
       </c>
       <c r="L5" t="n">
-        <v>3600000</v>
+        <v>485000</v>
       </c>
       <c r="M5" t="n">
-        <v>-3805000</v>
+        <v>-6950000</v>
       </c>
       <c r="N5" t="n">
-        <v>-100000000</v>
+        <v>-100077000</v>
       </c>
       <c r="O5" t="n">
-        <v>-100000000</v>
+        <v>-100077000</v>
       </c>
       <c r="P5" t="n">
-        <v>40400000</v>
+        <v>-94073000</v>
       </c>
       <c r="Q5" t="n">
-        <v>40400000</v>
+        <v>-94073000</v>
       </c>
       <c r="R5" t="n">
-        <v>-74226000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-74226000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-129597000</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>55371000</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-46450000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1492000</v>
-      </c>
+        <v>-133721000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>48554000</v>
+        <v>-15552000</v>
       </c>
       <c r="Y5" t="n">
-        <v>575894000</v>
+        <v>697009000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-527340000</v>
+        <v>-712561000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-71717000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2100000</v>
-      </c>
+        <v>-4000000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>-73817000</v>
+        <v>-4000000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-24779000</v>
+        <v>-114169000</v>
       </c>
       <c r="AE5" t="n">
-        <v>27000</v>
+        <v>22000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-24806000</v>
+        <v>-114191000</v>
       </c>
       <c r="AG5" t="n">
-        <v>213772000</v>
+        <v>257383000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-39642000</v>
+        <v>-48342000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-28074000</v>
+        <v>35592000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1716000</v>
+        <v>3967000</v>
       </c>
       <c r="AK5" t="n">
-        <v>28460000</v>
+        <v>34609000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-28160000</v>
+        <v>11288000</v>
       </c>
       <c r="AM5" t="n">
-        <v>7579000</v>
+        <v>8229000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-37669000</v>
+        <v>-22501000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1511000</v>
+        <v>6950000</v>
       </c>
       <c r="AP5" t="n">
-        <v>21813000</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>28414000</v>
+        <v>56416000</v>
       </c>
       <c r="AS5" t="n">
-        <v>272000</v>
+        <v>546000</v>
       </c>
       <c r="AT5" t="n">
-        <v>28142000</v>
+        <v>55870000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-2329000</v>
-      </c>
-      <c r="AV5" t="inlineStr"/>
+        <v>-2810000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>214000</v>
+      </c>
       <c r="AW5" t="n">
-        <v>-159000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-33000</v>
-      </c>
+        <v>-314000</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>230173000</v>
+        <v>206613000</v>
       </c>
     </row>
   </sheetData>
@@ -3919,187 +3919,187 @@
       </c>
       <c r="DI1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
         </is>
       </c>
       <c r="ET1" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Jian  Huang', 'age': 58, 'title': 'Executive Chairman of the Board of Directors', 'yearBorn': 1967, 'fiscalYear': 2024, 'totalPay': 2934332, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Youquan  Li', 'age': 50, 'title': 'GM &amp; Executive Director', 'yearBorn': 1975, 'fiscalYear': 2024, 'totalPay': 3950285, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wenbin  Zheng', 'age': 54, 'title': 'Executive Vice Chairman of the Board', 'yearBorn': 1971, 'fiscalYear': 2024, 'totalPay': 1258067, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Danyan  Huang', 'age': 62, 'title': 'Deputy GM &amp; Executive Director', 'yearBorn': 1963, 'fiscalYear': 2024, 'totalPay': 1055340, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhigao  Chen', 'age': 47, 'title': 'Deputy GM &amp; CFO', 'yearBorn': 1978, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kwan Wai  Leung', 'age': 42, 'title': 'Joint Company Secretary', 'yearBorn': 1983, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ting  Xiong', 'age': 44, 'title': 'Joint Company Secretary', 'yearBorn': 1981, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Huizhen  Weng', 'age': 51, 'title': 'Deputy General Manager', 'yearBorn': 1974, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Qunyan  Fan', 'age': 43, 'title': 'Deputy General Manager', 'yearBorn': 1982, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Liangjie  Li', 'age': 45, 'title': 'Deputy General Manager', 'yearBorn': 1980, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Jian  Huang', 'age': 58, 'title': 'Executive Chairman of the Board of Directors', 'yearBorn': 1967, 'fiscalYear': 2024, 'totalPay': 2931993, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Youquan  Li', 'age': 50, 'title': 'GM &amp; Executive Director', 'yearBorn': 1975, 'fiscalYear': 2024, 'totalPay': 3947137, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wenbin  Zheng', 'age': 54, 'title': 'Executive Vice Chairman of the Board', 'yearBorn': 1971, 'fiscalYear': 2024, 'totalPay': 1257065, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Danyan  Huang', 'age': 62, 'title': 'Deputy GM &amp; Executive Director', 'yearBorn': 1963, 'fiscalYear': 2024, 'totalPay': 1054499, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhigao  Chen', 'age': 47, 'title': 'Deputy GM &amp; CFO', 'yearBorn': 1978, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kwan Wai  Leung', 'age': 42, 'title': 'Joint Company Secretary', 'yearBorn': 1983, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ting  Xiong', 'age': 44, 'title': 'Joint Company Secretary', 'yearBorn': 1981, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Huizhen  Weng', 'age': 51, 'title': 'Deputy General Manager', 'yearBorn': 1974, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Qunyan  Fan', 'age': 43, 'title': 'Deputy General Manager', 'yearBorn': 1982, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Liangjie  Li', 'age': 45, 'title': 'Deputy General Manager', 'yearBorn': 1980, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4202,7 +4202,7 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>6.99</v>
+        <v>6.9</v>
       </c>
       <c r="V2" t="n">
         <v>6.96</v>
@@ -4214,7 +4214,7 @@
         <v>6.96</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.99</v>
+        <v>6.9</v>
       </c>
       <c r="Z2" t="n">
         <v>6.96</v>
@@ -4229,7 +4229,7 @@
         <v>0.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.37</v>
+        <v>4.41</v>
       </c>
       <c r="AE2" t="n">
         <v>1778716800</v>
@@ -4238,40 +4238,40 @@
         <v>0.5188</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.006</v>
       </c>
       <c r="AH2" t="n">
-        <v>14.808511</v>
+        <v>14.680851</v>
       </c>
       <c r="AI2" t="n">
-        <v>14.308636</v>
+        <v>14.192817</v>
       </c>
       <c r="AJ2" t="n">
-        <v>43600</v>
+        <v>400</v>
       </c>
       <c r="AK2" t="n">
-        <v>43600</v>
+        <v>400</v>
       </c>
       <c r="AL2" t="n">
-        <v>22816</v>
+        <v>23067</v>
       </c>
       <c r="AM2" t="n">
-        <v>1244</v>
+        <v>21320</v>
       </c>
       <c r="AN2" t="n">
-        <v>1244</v>
+        <v>21320</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.96</v>
+        <v>6.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3213384704</v>
+        <v>3185682944</v>
       </c>
       <c r="AR2" t="n">
-        <v>3213384672</v>
+        <v>3185683080</v>
       </c>
       <c r="AS2" t="n">
         <v>4.84</v>
@@ -4286,19 +4286,19 @@
         <v>4.84</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.6062354</v>
+        <v>1.5923885</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.9206</v>
+        <v>6.274</v>
       </c>
       <c r="AY2" t="n">
-        <v>6.58315</v>
+        <v>6.54565</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.266</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.038054366</v>
+        <v>0.038550723</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>2715836672</v>
+        <v>2688125952</v>
       </c>
       <c r="BE2" t="n">
         <v>0.09425</v>
@@ -4330,10 +4330,10 @@
         <v>461693200</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.032539</v>
+        <v>2.0314603</v>
       </c>
       <c r="BL2" t="n">
-        <v>3.4242887</v>
+        <v>3.3965714</v>
       </c>
       <c r="BM2" t="n">
         <v>1767139200</v>
@@ -4354,19 +4354,19 @@
         <v>0.47</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.48641956</v>
+        <v>0.48616144</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.358</v>
+        <v>1.344</v>
       </c>
       <c r="BU2" t="n">
-        <v>8.529999999999999</v>
+        <v>8.443</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.08749997599999999</v>
+        <v>0.0917722</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BX2" t="n">
         <v>0.303982</v>
@@ -4380,19 +4380,19 @@
         </is>
       </c>
       <c r="CA2" t="n">
-        <v>6.96</v>
+        <v>6.9</v>
       </c>
       <c r="CB2" t="n">
-        <v>7.0170345</v>
+        <v>7.006132</v>
       </c>
       <c r="CC2" t="n">
-        <v>7.0170345</v>
+        <v>7.006132</v>
       </c>
       <c r="CD2" t="n">
-        <v>7.0170345</v>
+        <v>7.006132</v>
       </c>
       <c r="CE2" t="n">
-        <v>7.0170345</v>
+        <v>7.006132</v>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
@@ -4499,137 +4499,137 @@
       </c>
       <c r="DI2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1781494469</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>finmb_1762136667</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DQ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>YAN PALACE</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>Xiamen Yan Palace Bird's Nest Industry Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DV2" t="n">
+        <v>0.48616144</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>16.82927</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.6259999000000001</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.09977684000000001</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.3543501</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.054135203</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>15</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="EG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>1702344600000</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>6.96 - 6.96</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="EL2" t="n">
+        <v>23067</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>0.4256198</v>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>4.84 - 8.78</t>
+        </is>
+      </c>
+      <c r="EP2" t="n">
+        <v>-1.8799996</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>-0.21412297</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>9.177218999999999</v>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
           <t>PRE</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>Xiamen Yan Palace Bird's Nest Industry Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>22816</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.4380165</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>4.84 - 8.78</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>-1.8199997</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.20728926</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>8.749998</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.48641956</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>16.97561</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.42918074</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>6.96</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>YAN PALACE</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>1780285692</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>finmb_1762136667</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1.0394001</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.17555656</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>0.37685013</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>0.05724465</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>1702344600000</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>-0.029999733</v>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>6.96 - 6.96</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr"/>
